--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0212.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0212.xlsx
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>"Ừ, không chơi trò nữa đâu! Mấy trò ma mãnh của ngươi làm sao qua mặt được ta và {PlayerName}! Ngươi đang bày trò gì thế?!"</t>
+          <t>"Ừ, không chơi trò nữa đâu! Mấy trò ma mãnh của mày làm sao qua mặt được tao và {PlayerName}! Mày đang bày trò gì thế?!"</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>"Cái quả bóng bé tí này đang nói gì vậy? Được rồi, được rồi. Ta thừa nhận. Ta là người chỉ huy ở đây."</t>
+          <t>"Cái quả bóng bé tí này đang nói gì vậy? Được rồi, được rồi. Tao thừa nhận. Tao là người chỉ huy ở đây."</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Cũng không phải như ta mới gặp ngươi ngày hôm qua...</t>
+          <t>Cũng không phải như tao mới gặp mày ngày hôm qua...</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>[Lời Cuối Cùng] Ta sẽ đi quan sát mấy đứa săn tumbleyak.</t>
+          <t>[Lời Cuối Cùng] Tao sẽ đi quan sát mấy đứa săn tumbleyak.</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>"Chọn số bằng máy thì có ý nghĩa gì chứ? Máy móc là do bọn xổ số làm ra! Cậu thật sự nghĩ chúng nó sẽ để cậu trúng à?"</t>
+          <t>"Chọn số bằng máy thì có ý nghĩa gì chứ? Máy móc là do bọn xổ số làm ra! Mày thật sự nghĩ chúng nó sẽ để mày trúng à?"</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>"Thật là đồ vô ơn. Ta chỉ định giúp ngươi thôi mà... Ta sẽ chọn số bằng máy luôn cho rồi."</t>
+          <t>"Thật là đồ vô ơn. Tao chỉ định giúp mày thôi mà... Tao sẽ chọn số bằng máy luôn cho rồi."</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>[Lời Cuối Cùng] Ta ghét những tình huống tiến thoái lưỡng nan kiểu này.</t>
+          <t>[Lời Cuối Cùng] Tao ghét những tình huống tiến thoái lưỡng nan kiểu này.</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>"Nếu ta dừng bước chỉ vì những điều xấu xa trước mắt... thì chút đẹp đẽ còn sót lại cũng sẽ bị hủy diệt theo."</t>
+          <t>"Nếu tao dừng bước chỉ vì những điều xấu xa trước mắt... thì chút đẹp đẽ còn sót lại cũng sẽ bị hủy diệt theo."</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>"Nếu là cậu... ta biết... ta biết cậu có thể tìm ra một kết thúc mới cho câu chuyện..."</t>
+          <t>"Nếu là cậu... tao biết... tao biết cậu có thể tìm ra một kết thúc mới cho câu chuyện..."</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>"Gửi lời chào của ta đến {Male=chàng trai tóc đen;Female=cô nàng tóc đen} kia đi."</t>
+          <t>"Gửi lời chào của ta đến {Male=young man;Female=young lady} kia đi."</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Tăng Trạng Thái] Cho ta xem hàng của ngươi.</t>
+          <t>Tăng Trạng Thái] Cho tao xem hàng của mày.</t>
         </is>
       </c>
     </row>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>[Lời Cuối Cùng] Đưa hết đồ của cậu đây! Tất cả!</t>
+          <t>[Lời Cuối Cùng] Đưa hết đồ của mày đây! Tất cả!</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>"...Thôi nào, ta chẳng hiểu nổi cái gì cả. Ngươi tính tiền theo từng chữ à?"</t>
+          <t>"...Thôi nào, tao chẳng hiểu nổi cái gì cả. Mày tính tiền theo từng chữ à?"</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>"Ra vậy. Thì ra cậu cũng thuộc loại chỉ biết nghĩ cho bản thân."</t>
+          <t>"Ra vậy. Thì ra mày cũng thuộc loại chỉ biết nghĩ cho bản thân."</t>
         </is>
       </c>
     </row>
